--- a/data/WP17/WP17_auswertung_sachgebiete.xlsx
+++ b/data/WP17/WP17_auswertung_sachgebiete.xlsx
@@ -848,16 +848,16 @@
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D2" t="n">
-        <v>31.1920138888889</v>
+        <v>31.1442441054092</v>
       </c>
       <c r="E2" t="n">
         <v>441</v>
       </c>
       <c r="F2" t="n">
-        <v>38.75</v>
+        <v>38.8349514563107</v>
       </c>
     </row>
     <row r="3">
@@ -891,13 +891,13 @@
         <v>516</v>
       </c>
       <c r="D4" t="n">
-        <v>31.6631136950904</v>
+        <v>31.6531007751938</v>
       </c>
       <c r="E4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F4" t="n">
-        <v>30.8139534883721</v>
+        <v>30.4263565891473</v>
       </c>
     </row>
     <row r="5">
@@ -911,7 +911,7 @@
         <v>499</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2631313046261</v>
+        <v>30.2605210420842</v>
       </c>
       <c r="E5" t="n">
         <v>291</v>
@@ -1228,16 +1228,16 @@
         <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" t="n">
-        <v>31.3716216216216</v>
+        <v>31.4362416107383</v>
       </c>
       <c r="E21" t="n">
         <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>41.2162162162162</v>
+        <v>41.6107382550336</v>
       </c>
     </row>
     <row r="22">
@@ -1491,13 +1491,13 @@
         <v>89</v>
       </c>
       <c r="D34" t="n">
-        <v>31.6982343499197</v>
+        <v>31.6292134831461</v>
       </c>
       <c r="E34" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>41.5730337078652</v>
+        <v>39.3258426966292</v>
       </c>
     </row>
     <row r="35">
@@ -1731,7 +1731,7 @@
         <v>73</v>
       </c>
       <c r="D46" t="n">
-        <v>39.7671232876712</v>
+        <v>39.5753424657534</v>
       </c>
       <c r="E46" t="n">
         <v>63</v>
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{210354A8-2E52-48F0-A0AA-B6A98D961F96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48A1B8B-29DE-4366-BFC7-96E2A555BEB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586948B9-D37D-4364-89B3-14B3AA5CBBA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBB88EA-E52C-4F02-8F82-F082B91528C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CC7F5EF-30E8-4BE6-9EFC-7FAC2D9D2687}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858C418B-921E-4F80-BD71-9FA5A1530379}"/>
 </file>
--- a/data/WP17/WP17_auswertung_sachgebiete.xlsx
+++ b/data/WP17/WP17_auswertung_sachgebiete.xlsx
@@ -851,13 +851,13 @@
         <v>721</v>
       </c>
       <c r="D2" t="n">
-        <v>31.1442441054092</v>
+        <v>31.5492371705964</v>
       </c>
       <c r="E2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F2" t="n">
-        <v>38.8349514563107</v>
+        <v>38.6962552011096</v>
       </c>
     </row>
     <row r="3">
@@ -871,13 +871,13 @@
         <v>699</v>
       </c>
       <c r="D3" t="n">
-        <v>34.343347639485</v>
+        <v>34.3419170243205</v>
       </c>
       <c r="E3" t="n">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F3" t="n">
-        <v>32.618025751073</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -891,13 +891,13 @@
         <v>516</v>
       </c>
       <c r="D4" t="n">
-        <v>31.6531007751938</v>
+        <v>31.5639534883721</v>
       </c>
       <c r="E4" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F4" t="n">
-        <v>30.4263565891473</v>
+        <v>29.0697674418605</v>
       </c>
     </row>
     <row r="5">
@@ -911,13 +911,13 @@
         <v>499</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2605210420842</v>
+        <v>29.6713426853707</v>
       </c>
       <c r="E5" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F5" t="n">
-        <v>41.6833667334669</v>
+        <v>43.2865731462926</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>405</v>
       </c>
       <c r="D6" t="n">
-        <v>32.1901234567901</v>
+        <v>32.0049382716049</v>
       </c>
       <c r="E6" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F6" t="n">
-        <v>32.3456790123457</v>
+        <v>32.0987654320988</v>
       </c>
     </row>
     <row r="7">
@@ -951,13 +951,13 @@
         <v>404</v>
       </c>
       <c r="D7" t="n">
-        <v>34.9777227722772</v>
+        <v>33.5915841584158</v>
       </c>
       <c r="E7" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="F7" t="n">
-        <v>15.8415841584158</v>
+        <v>28.2178217821782</v>
       </c>
     </row>
     <row r="8">
@@ -971,13 +971,13 @@
         <v>392</v>
       </c>
       <c r="D8" t="n">
-        <v>33.030612244898</v>
+        <v>32.4617346938776</v>
       </c>
       <c r="E8" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="F8" t="n">
-        <v>29.0816326530612</v>
+        <v>32.6530612244898</v>
       </c>
     </row>
     <row r="9">
@@ -991,13 +991,13 @@
         <v>368</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7554347826087</v>
+        <v>29.7228260869565</v>
       </c>
       <c r="E9" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F9" t="n">
-        <v>42.3913043478261</v>
+        <v>41.5760869565217</v>
       </c>
     </row>
     <row r="10">
@@ -1011,13 +1011,13 @@
         <v>346</v>
       </c>
       <c r="D10" t="n">
-        <v>31.6387283236994</v>
+        <v>32.0838150289017</v>
       </c>
       <c r="E10" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F10" t="n">
-        <v>36.4161849710983</v>
+        <v>33.8150289017341</v>
       </c>
     </row>
     <row r="11">
@@ -1031,13 +1031,13 @@
         <v>305</v>
       </c>
       <c r="D11" t="n">
-        <v>30.9639344262295</v>
+        <v>31.4032786885246</v>
       </c>
       <c r="E11" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F11" t="n">
-        <v>37.3770491803279</v>
+        <v>35.0819672131148</v>
       </c>
     </row>
     <row r="12">
@@ -1051,13 +1051,13 @@
         <v>291</v>
       </c>
       <c r="D12" t="n">
-        <v>30.7766323024055</v>
+        <v>30.701030927835</v>
       </c>
       <c r="E12" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F12" t="n">
-        <v>26.8041237113402</v>
+        <v>25.7731958762887</v>
       </c>
     </row>
     <row r="13">
@@ -1071,13 +1071,13 @@
         <v>272</v>
       </c>
       <c r="D13" t="n">
-        <v>30.8308823529412</v>
+        <v>30.9779411764706</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F13" t="n">
-        <v>49.6323529411765</v>
+        <v>47.7941176470588</v>
       </c>
     </row>
     <row r="14">
@@ -1091,13 +1091,13 @@
         <v>221</v>
       </c>
       <c r="D14" t="n">
-        <v>36.8371040723982</v>
+        <v>36.6515837104072</v>
       </c>
       <c r="E14" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F14" t="n">
-        <v>20.3619909502262</v>
+        <v>19.0045248868778</v>
       </c>
     </row>
     <row r="15">
@@ -1111,13 +1111,13 @@
         <v>192</v>
       </c>
       <c r="D15" t="n">
-        <v>34.6875</v>
+        <v>34.203125</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>32.2916666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -1131,13 +1131,13 @@
         <v>189</v>
       </c>
       <c r="D16" t="n">
-        <v>36.6825396825397</v>
+        <v>36.1375661375661</v>
       </c>
       <c r="E16" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F16" t="n">
-        <v>14.2857142857143</v>
+        <v>15.3439153439153</v>
       </c>
     </row>
     <row r="17">
@@ -1151,13 +1151,13 @@
         <v>184</v>
       </c>
       <c r="D17" t="n">
-        <v>32.9076086956522</v>
+        <v>32.6304347826087</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
-        <v>34.7826086956522</v>
+        <v>36.4130434782609</v>
       </c>
     </row>
     <row r="18">
@@ -1171,13 +1171,13 @@
         <v>178</v>
       </c>
       <c r="D18" t="n">
-        <v>34.6460674157303</v>
+        <v>34.2191011235955</v>
       </c>
       <c r="E18" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F18" t="n">
-        <v>28.6516853932584</v>
+        <v>29.2134831460674</v>
       </c>
     </row>
     <row r="19">
@@ -1191,13 +1191,13 @@
         <v>155</v>
       </c>
       <c r="D19" t="n">
-        <v>34.8451612903226</v>
+        <v>32.1870967741935</v>
       </c>
       <c r="E19" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F19" t="n">
-        <v>10.3225806451613</v>
+        <v>18.0645161290323</v>
       </c>
     </row>
     <row r="20">
@@ -1211,13 +1211,13 @@
         <v>154</v>
       </c>
       <c r="D20" t="n">
-        <v>30.5584415584416</v>
+        <v>30.8896103896104</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F20" t="n">
-        <v>45.4545454545455</v>
+        <v>40.2597402597403</v>
       </c>
     </row>
     <row r="21">
@@ -1231,13 +1231,13 @@
         <v>149</v>
       </c>
       <c r="D21" t="n">
-        <v>31.4362416107383</v>
+        <v>31.1073825503356</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F21" t="n">
-        <v>41.6107382550336</v>
+        <v>44.2953020134228</v>
       </c>
     </row>
     <row r="22">
@@ -1254,10 +1254,10 @@
         <v>33.669014084507</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>33.8028169014084</v>
+        <v>33.0985915492958</v>
       </c>
     </row>
     <row r="23">
@@ -1271,13 +1271,13 @@
         <v>141</v>
       </c>
       <c r="D23" t="n">
-        <v>30.9787234042553</v>
+        <v>30.6170212765957</v>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>48.2269503546099</v>
+        <v>48.936170212766</v>
       </c>
     </row>
     <row r="24">
@@ -1291,13 +1291,13 @@
         <v>138</v>
       </c>
       <c r="D24" t="n">
-        <v>31.1521739130435</v>
+        <v>31.6666666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>34.7826086956522</v>
+        <v>31.1594202898551</v>
       </c>
     </row>
     <row r="25">
@@ -1311,13 +1311,13 @@
         <v>130</v>
       </c>
       <c r="D25" t="n">
-        <v>30.6461538461538</v>
+        <v>30.7153846153846</v>
       </c>
       <c r="E25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" t="n">
-        <v>52.3076923076923</v>
+        <v>51.5384615384615</v>
       </c>
     </row>
     <row r="26">
@@ -1331,13 +1331,13 @@
         <v>119</v>
       </c>
       <c r="D26" t="n">
-        <v>30.1932773109244</v>
+        <v>30.8319327731092</v>
       </c>
       <c r="E26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
-        <v>47.8991596638655</v>
+        <v>47.0588235294118</v>
       </c>
     </row>
     <row r="27">
@@ -1351,13 +1351,13 @@
         <v>114</v>
       </c>
       <c r="D27" t="n">
-        <v>32.1140350877193</v>
+        <v>32.6228070175439</v>
       </c>
       <c r="E27" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>25.4385964912281</v>
+        <v>24.5614035087719</v>
       </c>
     </row>
     <row r="28">
@@ -1371,13 +1371,13 @@
         <v>114</v>
       </c>
       <c r="D28" t="n">
-        <v>30.2368421052632</v>
+        <v>30.1315789473684</v>
       </c>
       <c r="E28" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F28" t="n">
-        <v>42.1052631578947</v>
+        <v>44.7368421052632</v>
       </c>
     </row>
     <row r="29">
@@ -1391,13 +1391,13 @@
         <v>112</v>
       </c>
       <c r="D29" t="n">
-        <v>30.0089285714286</v>
+        <v>29.0357142857143</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>47.3214285714286</v>
+        <v>48.2142857142857</v>
       </c>
     </row>
     <row r="30">
@@ -1411,13 +1411,13 @@
         <v>104</v>
       </c>
       <c r="D30" t="n">
-        <v>29.3269230769231</v>
+        <v>29.1923076923077</v>
       </c>
       <c r="E30" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F30" t="n">
-        <v>38.4615384615385</v>
+        <v>41.3461538461538</v>
       </c>
     </row>
     <row r="31">
@@ -1431,13 +1431,13 @@
         <v>101</v>
       </c>
       <c r="D31" t="n">
-        <v>34.9405940594059</v>
+        <v>35.6237623762376</v>
       </c>
       <c r="E31" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F31" t="n">
-        <v>21.7821782178218</v>
+        <v>17.8217821782178</v>
       </c>
     </row>
     <row r="32">
@@ -1451,13 +1451,13 @@
         <v>94</v>
       </c>
       <c r="D32" t="n">
-        <v>23.4893617021277</v>
+        <v>22.968085106383</v>
       </c>
       <c r="E32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>84.0425531914894</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="33">
@@ -1471,7 +1471,7 @@
         <v>92</v>
       </c>
       <c r="D33" t="n">
-        <v>26.5434782608696</v>
+        <v>26.2282608695652</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1491,13 +1491,13 @@
         <v>89</v>
       </c>
       <c r="D34" t="n">
-        <v>31.6292134831461</v>
+        <v>31.8539325842697</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F34" t="n">
-        <v>39.3258426966292</v>
+        <v>34.8314606741573</v>
       </c>
     </row>
     <row r="35">
@@ -1511,13 +1511,13 @@
         <v>88</v>
       </c>
       <c r="D35" t="n">
-        <v>31.1136363636364</v>
+        <v>31.9318181818182</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F35" t="n">
-        <v>31.8181818181818</v>
+        <v>32.9545454545455</v>
       </c>
     </row>
     <row r="36">
@@ -1531,13 +1531,13 @@
         <v>87</v>
       </c>
       <c r="D36" t="n">
-        <v>35.7701149425287</v>
+        <v>35.2413793103448</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2413793103448</v>
+        <v>18.3908045977011</v>
       </c>
     </row>
     <row r="37">
@@ -1551,7 +1551,7 @@
         <v>87</v>
       </c>
       <c r="D37" t="n">
-        <v>28.5172413793103</v>
+        <v>28.3448275862069</v>
       </c>
       <c r="E37" t="n">
         <v>34</v>
@@ -1571,7 +1571,7 @@
         <v>84</v>
       </c>
       <c r="D38" t="n">
-        <v>30.6071428571429</v>
+        <v>31.8928571428571</v>
       </c>
       <c r="E38" t="n">
         <v>48</v>
@@ -1591,13 +1591,13 @@
         <v>83</v>
       </c>
       <c r="D39" t="n">
-        <v>29.2650602409639</v>
+        <v>29.2168674698795</v>
       </c>
       <c r="E39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F39" t="n">
-        <v>54.2168674698795</v>
+        <v>53.0120481927711</v>
       </c>
     </row>
     <row r="40">
@@ -1611,7 +1611,7 @@
         <v>82</v>
       </c>
       <c r="D40" t="n">
-        <v>26.5731707317073</v>
+        <v>25.3414634146341</v>
       </c>
       <c r="E40" t="n">
         <v>25</v>
@@ -1631,13 +1631,13 @@
         <v>81</v>
       </c>
       <c r="D41" t="n">
-        <v>32.3086419753086</v>
+        <v>31.7283950617284</v>
       </c>
       <c r="E41" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F41" t="n">
-        <v>28.3950617283951</v>
+        <v>35.8024691358025</v>
       </c>
     </row>
     <row r="42">
@@ -1651,13 +1651,13 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>32.5875</v>
+        <v>31.6625</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="43">
@@ -1671,13 +1671,13 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>31.5</v>
+        <v>31.3589743589744</v>
       </c>
       <c r="E43" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F43" t="n">
-        <v>30.7692307692308</v>
+        <v>29.4871794871795</v>
       </c>
     </row>
     <row r="44">
@@ -1691,13 +1691,13 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>27.9342105263158</v>
+        <v>27.3815789473684</v>
       </c>
       <c r="E44" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
-        <v>65.7894736842105</v>
+        <v>69.7368421052632</v>
       </c>
     </row>
     <row r="45">
@@ -1711,7 +1711,7 @@
         <v>76</v>
       </c>
       <c r="D45" t="n">
-        <v>34.5</v>
+        <v>34.1447368421053</v>
       </c>
       <c r="E45" t="n">
         <v>57</v>
@@ -1731,13 +1731,13 @@
         <v>73</v>
       </c>
       <c r="D46" t="n">
-        <v>39.5753424657534</v>
+        <v>39.1917808219178</v>
       </c>
       <c r="E46" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F46" t="n">
-        <v>13.6986301369863</v>
+        <v>10.958904109589</v>
       </c>
     </row>
     <row r="47">
@@ -1751,13 +1751,13 @@
         <v>71</v>
       </c>
       <c r="D47" t="n">
-        <v>34.5915492957746</v>
+        <v>33.9718309859155</v>
       </c>
       <c r="E47" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F47" t="n">
-        <v>28.169014084507</v>
+        <v>33.8028169014084</v>
       </c>
     </row>
     <row r="48">
@@ -1771,13 +1771,13 @@
         <v>70</v>
       </c>
       <c r="D48" t="n">
-        <v>27.9714285714286</v>
+        <v>24.6571428571429</v>
       </c>
       <c r="E48" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>27.1428571428572</v>
+        <v>92.8571428571429</v>
       </c>
     </row>
     <row r="49">
@@ -1791,7 +1791,7 @@
         <v>69</v>
       </c>
       <c r="D49" t="n">
-        <v>31.2898550724638</v>
+        <v>31.231884057971</v>
       </c>
       <c r="E49" t="n">
         <v>42</v>
@@ -1811,13 +1811,13 @@
         <v>67</v>
       </c>
       <c r="D50" t="n">
-        <v>31.5074626865672</v>
+        <v>31.865671641791</v>
       </c>
       <c r="E50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>35.8208955223881</v>
+        <v>37.3134328358209</v>
       </c>
     </row>
     <row r="51">
@@ -1831,7 +1831,7 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>34.8125</v>
+        <v>35.640625</v>
       </c>
       <c r="E51" t="n">
         <v>54</v>
@@ -1851,7 +1851,7 @@
         <v>63</v>
       </c>
       <c r="D52" t="n">
-        <v>32.1904761904762</v>
+        <v>32.1428571428571</v>
       </c>
       <c r="E52" t="n">
         <v>39</v>
@@ -1871,13 +1871,13 @@
         <v>62</v>
       </c>
       <c r="D53" t="n">
-        <v>31.2903225806452</v>
+        <v>31.258064516129</v>
       </c>
       <c r="E53" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F53" t="n">
-        <v>41.9354838709677</v>
+        <v>40.3225806451613</v>
       </c>
     </row>
     <row r="54">
@@ -1891,13 +1891,13 @@
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>33.0322580645161</v>
+        <v>33.6935483870968</v>
       </c>
       <c r="E54" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>35.4838709677419</v>
+        <v>40.3225806451613</v>
       </c>
     </row>
     <row r="55">
@@ -1911,13 +1911,13 @@
         <v>61</v>
       </c>
       <c r="D55" t="n">
-        <v>30.5737704918033</v>
+        <v>32.0819672131148</v>
       </c>
       <c r="E55" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F55" t="n">
-        <v>45.9016393442623</v>
+        <v>40.983606557377</v>
       </c>
     </row>
     <row r="56">
@@ -1931,13 +1931,13 @@
         <v>60</v>
       </c>
       <c r="D56" t="n">
-        <v>30.8333333333333</v>
+        <v>31.1666666666667</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F56" t="n">
-        <v>30</v>
+        <v>31.6666666666667</v>
       </c>
     </row>
     <row r="57">
@@ -1951,13 +1951,13 @@
         <v>60</v>
       </c>
       <c r="D57" t="n">
-        <v>31.9666666666667</v>
+        <v>32.4833333333333</v>
       </c>
       <c r="E57" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F57" t="n">
-        <v>40</v>
+        <v>31.6666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -1971,7 +1971,7 @@
         <v>59</v>
       </c>
       <c r="D58" t="n">
-        <v>38.1864406779661</v>
+        <v>37.5762711864407</v>
       </c>
       <c r="E58" t="n">
         <v>50</v>
@@ -1991,13 +1991,13 @@
         <v>55</v>
       </c>
       <c r="D59" t="n">
-        <v>29.8727272727273</v>
+        <v>29.9818181818182</v>
       </c>
       <c r="E59" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F59" t="n">
-        <v>45.4545454545455</v>
+        <v>43.6363636363636</v>
       </c>
     </row>
     <row r="60">
@@ -2011,13 +2011,13 @@
         <v>54</v>
       </c>
       <c r="D60" t="n">
-        <v>30.1481481481481</v>
+        <v>30.037037037037</v>
       </c>
       <c r="E60" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F60" t="n">
-        <v>46.2962962962963</v>
+        <v>42.5925925925926</v>
       </c>
     </row>
     <row r="61">
@@ -2031,7 +2031,7 @@
         <v>52</v>
       </c>
       <c r="D61" t="n">
-        <v>36.9230769230769</v>
+        <v>36.1538461538462</v>
       </c>
       <c r="E61" t="n">
         <v>47</v>
@@ -2051,13 +2051,13 @@
         <v>52</v>
       </c>
       <c r="D62" t="n">
-        <v>29.5192307692308</v>
+        <v>29.7692307692308</v>
       </c>
       <c r="E62" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F62" t="n">
-        <v>36.5384615384615</v>
+        <v>40.3846153846154</v>
       </c>
     </row>
     <row r="63">
@@ -2071,13 +2071,13 @@
         <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>29.44</v>
+        <v>28.28</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64">
@@ -2091,13 +2091,13 @@
         <v>48</v>
       </c>
       <c r="D64" t="n">
-        <v>33.8125</v>
+        <v>34.1666666666667</v>
       </c>
       <c r="E64" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>29.1666666666667</v>
+        <v>27.0833333333333</v>
       </c>
     </row>
     <row r="65">
@@ -2111,13 +2111,13 @@
         <v>42</v>
       </c>
       <c r="D65" t="n">
-        <v>31.9285714285714</v>
+        <v>31.2857142857143</v>
       </c>
       <c r="E65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F65" t="n">
-        <v>35.7142857142857</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="66">
@@ -2131,13 +2131,13 @@
         <v>41</v>
       </c>
       <c r="D66" t="n">
-        <v>30.0975609756098</v>
+        <v>30.1219512195122</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F66" t="n">
-        <v>51.219512195122</v>
+        <v>53.6585365853659</v>
       </c>
     </row>
     <row r="67">
@@ -2151,13 +2151,13 @@
         <v>39</v>
       </c>
       <c r="D67" t="n">
-        <v>32.7948717948718</v>
+        <v>32.4871794871795</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F67" t="n">
-        <v>35.8974358974359</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="68">
@@ -2171,13 +2171,13 @@
         <v>38</v>
       </c>
       <c r="D68" t="n">
-        <v>32.2631578947368</v>
+        <v>33</v>
       </c>
       <c r="E68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>39.4736842105263</v>
+        <v>36.8421052631579</v>
       </c>
     </row>
     <row r="69">
@@ -2191,13 +2191,13 @@
         <v>37</v>
       </c>
       <c r="D69" t="n">
-        <v>32.5405405405405</v>
+        <v>31.8378378378378</v>
       </c>
       <c r="E69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F69" t="n">
-        <v>37.8378378378378</v>
+        <v>40.5405405405405</v>
       </c>
     </row>
     <row r="70">
@@ -2211,7 +2211,7 @@
         <v>37</v>
       </c>
       <c r="D70" t="n">
-        <v>35.8378378378378</v>
+        <v>35.5945945945946</v>
       </c>
       <c r="E70" t="n">
         <v>26</v>
@@ -2231,13 +2231,13 @@
         <v>36</v>
       </c>
       <c r="D71" t="n">
-        <v>30.5</v>
+        <v>30.9722222222222</v>
       </c>
       <c r="E71" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F71" t="n">
-        <v>58.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -2251,7 +2251,7 @@
         <v>35</v>
       </c>
       <c r="D72" t="n">
-        <v>28.9428571428571</v>
+        <v>29</v>
       </c>
       <c r="E72" t="n">
         <v>15</v>
@@ -2271,13 +2271,13 @@
         <v>35</v>
       </c>
       <c r="D73" t="n">
-        <v>33.4</v>
+        <v>34.1142857142857</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F73" t="n">
-        <v>25.7142857142857</v>
+        <v>22.8571428571428</v>
       </c>
     </row>
     <row r="74">
@@ -2291,13 +2291,13 @@
         <v>33</v>
       </c>
       <c r="D74" t="n">
-        <v>32.4848484848485</v>
+        <v>32.3333333333333</v>
       </c>
       <c r="E74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" t="n">
-        <v>39.3939393939394</v>
+        <v>36.3636363636364</v>
       </c>
     </row>
     <row r="75">
@@ -2311,13 +2311,13 @@
         <v>33</v>
       </c>
       <c r="D75" t="n">
-        <v>31.3030303030303</v>
+        <v>30.9090909090909</v>
       </c>
       <c r="E75" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
-        <v>24.2424242424242</v>
+        <v>30.3030303030303</v>
       </c>
     </row>
     <row r="76">
@@ -2331,13 +2331,13 @@
         <v>33</v>
       </c>
       <c r="D76" t="n">
-        <v>31.1515151515152</v>
+        <v>31.2727272727273</v>
       </c>
       <c r="E76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F76" t="n">
-        <v>30.3030303030303</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="77">
@@ -2351,7 +2351,7 @@
         <v>33</v>
       </c>
       <c r="D77" t="n">
-        <v>28.4545454545455</v>
+        <v>29.030303030303</v>
       </c>
       <c r="E77" t="n">
         <v>14</v>
@@ -2371,13 +2371,13 @@
         <v>32</v>
       </c>
       <c r="D78" t="n">
-        <v>27.40625</v>
+        <v>28.65625</v>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F78" t="n">
-        <v>59.375</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="79">
@@ -2391,13 +2391,13 @@
         <v>31</v>
       </c>
       <c r="D79" t="n">
-        <v>31.3225806451613</v>
+        <v>32.3548387096774</v>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F79" t="n">
-        <v>35.4838709677419</v>
+        <v>29.0322580645161</v>
       </c>
     </row>
     <row r="80">
@@ -2411,13 +2411,13 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>34.6451612903226</v>
+        <v>36.2903225806452</v>
       </c>
       <c r="E80" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>32.258064516129</v>
+        <v>35.4838709677419</v>
       </c>
     </row>
     <row r="81">
@@ -2431,13 +2431,13 @@
         <v>30</v>
       </c>
       <c r="D81" t="n">
-        <v>28.2333333333333</v>
+        <v>28.5333333333333</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F81" t="n">
-        <v>70</v>
+        <v>63.3333333333333</v>
       </c>
     </row>
     <row r="82">
@@ -2451,13 +2451,13 @@
         <v>29</v>
       </c>
       <c r="D82" t="n">
-        <v>30.2413793103448</v>
+        <v>29.6896551724138</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>44.8275862068966</v>
+        <v>48.2758620689655</v>
       </c>
     </row>
     <row r="83">
@@ -2471,7 +2471,7 @@
         <v>29</v>
       </c>
       <c r="D83" t="n">
-        <v>29.5862068965517</v>
+        <v>29.7241379310345</v>
       </c>
       <c r="E83" t="n">
         <v>14</v>
@@ -2491,13 +2491,13 @@
         <v>27</v>
       </c>
       <c r="D84" t="n">
-        <v>30.4444444444444</v>
+        <v>30.2592592592593</v>
       </c>
       <c r="E84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F84" t="n">
-        <v>37.037037037037</v>
+        <v>40.7407407407407</v>
       </c>
     </row>
     <row r="85">
@@ -2511,7 +2511,7 @@
         <v>26</v>
       </c>
       <c r="D85" t="n">
-        <v>34.4615384615385</v>
+        <v>34.5769230769231</v>
       </c>
       <c r="E85" t="n">
         <v>19</v>
@@ -2531,13 +2531,13 @@
         <v>26</v>
       </c>
       <c r="D86" t="n">
-        <v>35.9230769230769</v>
+        <v>35.7692307692308</v>
       </c>
       <c r="E86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F86" t="n">
-        <v>34.6153846153846</v>
+        <v>30.7692307692308</v>
       </c>
     </row>
     <row r="87">
@@ -2551,7 +2551,7 @@
         <v>26</v>
       </c>
       <c r="D87" t="n">
-        <v>32.5384615384615</v>
+        <v>32.8846153846154</v>
       </c>
       <c r="E87" t="n">
         <v>20</v>
@@ -2571,13 +2571,13 @@
         <v>26</v>
       </c>
       <c r="D88" t="n">
-        <v>32.6153846153846</v>
+        <v>32.5384615384615</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>30.7692307692308</v>
+        <v>42.3076923076923</v>
       </c>
     </row>
     <row r="89">
@@ -2591,7 +2591,7 @@
         <v>25</v>
       </c>
       <c r="D89" t="n">
-        <v>32.96</v>
+        <v>34.12</v>
       </c>
       <c r="E89" t="n">
         <v>17</v>
@@ -2611,13 +2611,13 @@
         <v>25</v>
       </c>
       <c r="D90" t="n">
-        <v>35</v>
+        <v>34.56</v>
       </c>
       <c r="E90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F90" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
@@ -2631,13 +2631,13 @@
         <v>23</v>
       </c>
       <c r="D91" t="n">
-        <v>32.9565217391304</v>
+        <v>32.3913043478261</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
-        <v>43.4782608695652</v>
+        <v>47.8260869565217</v>
       </c>
     </row>
     <row r="92">
@@ -2651,7 +2651,7 @@
         <v>21</v>
       </c>
       <c r="D92" t="n">
-        <v>32</v>
+        <v>32.2380952380952</v>
       </c>
       <c r="E92" t="n">
         <v>12</v>
@@ -2671,13 +2671,13 @@
         <v>21</v>
       </c>
       <c r="D93" t="n">
-        <v>31.952380952381</v>
+        <v>32.7142857142857</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F93" t="n">
-        <v>23.8095238095238</v>
+        <v>19.047619047619</v>
       </c>
     </row>
     <row r="94">
@@ -2691,13 +2691,13 @@
         <v>20</v>
       </c>
       <c r="D94" t="n">
-        <v>34.3</v>
+        <v>33.25</v>
       </c>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
@@ -2711,7 +2711,7 @@
         <v>19</v>
       </c>
       <c r="D95" t="n">
-        <v>30.1052631578947</v>
+        <v>30.7894736842105</v>
       </c>
       <c r="E95" t="n">
         <v>12</v>
@@ -2731,13 +2731,13 @@
         <v>18</v>
       </c>
       <c r="D96" t="n">
-        <v>30.1111111111111</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="E96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>55.5555555555556</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
@@ -2751,7 +2751,7 @@
         <v>18</v>
       </c>
       <c r="D97" t="n">
-        <v>29</v>
+        <v>29.3333333333333</v>
       </c>
       <c r="E97" t="n">
         <v>9</v>
@@ -2771,7 +2771,7 @@
         <v>16</v>
       </c>
       <c r="D98" t="n">
-        <v>37.9375</v>
+        <v>37.125</v>
       </c>
       <c r="E98" t="n">
         <v>14</v>
@@ -2794,10 +2794,10 @@
         <v>27</v>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F99" t="n">
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="100">
@@ -2811,13 +2811,13 @@
         <v>16</v>
       </c>
       <c r="D100" t="n">
-        <v>31.125</v>
+        <v>30.0625</v>
       </c>
       <c r="E100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F100" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -2831,13 +2831,13 @@
         <v>16</v>
       </c>
       <c r="D101" t="n">
-        <v>36.1875</v>
+        <v>36.4375</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F101" t="n">
-        <v>31.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="102">
@@ -2851,7 +2851,7 @@
         <v>16</v>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>24.9375</v>
       </c>
       <c r="E102" t="n">
         <v>3</v>
@@ -2871,7 +2871,7 @@
         <v>15</v>
       </c>
       <c r="D103" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="E103" t="n">
         <v>9</v>
@@ -2891,13 +2891,13 @@
         <v>15</v>
       </c>
       <c r="D104" t="n">
-        <v>35.4</v>
+        <v>33.9333333333333</v>
       </c>
       <c r="E104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F104" t="n">
-        <v>26.6666666666667</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105">
@@ -2911,13 +2911,13 @@
         <v>14</v>
       </c>
       <c r="D105" t="n">
-        <v>27.7142857142857</v>
+        <v>27.5</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F105" t="n">
-        <v>64.2857142857143</v>
+        <v>71.4285714285714</v>
       </c>
     </row>
     <row r="106">
@@ -2931,7 +2931,7 @@
         <v>14</v>
       </c>
       <c r="D106" t="n">
-        <v>29.4285714285714</v>
+        <v>30.0714285714286</v>
       </c>
       <c r="E106" t="n">
         <v>7</v>
@@ -2951,13 +2951,13 @@
         <v>14</v>
       </c>
       <c r="D107" t="n">
-        <v>29.7142857142857</v>
+        <v>30.2857142857143</v>
       </c>
       <c r="E107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F107" t="n">
-        <v>50</v>
+        <v>57.1428571428571</v>
       </c>
     </row>
     <row r="108">
@@ -2971,13 +2971,13 @@
         <v>14</v>
       </c>
       <c r="D108" t="n">
-        <v>32.5</v>
+        <v>32.6428571428571</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>28.5714285714286</v>
+        <v>21.4285714285714</v>
       </c>
     </row>
     <row r="109">
@@ -2991,7 +2991,7 @@
         <v>14</v>
       </c>
       <c r="D109" t="n">
-        <v>32.2857142857143</v>
+        <v>31.8571428571429</v>
       </c>
       <c r="E109" t="n">
         <v>9</v>
@@ -3011,13 +3011,13 @@
         <v>13</v>
       </c>
       <c r="D110" t="n">
-        <v>25.8461538461538</v>
+        <v>25.3076923076923</v>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F110" t="n">
-        <v>69.2307692307692</v>
+        <v>76.9230769230769</v>
       </c>
     </row>
     <row r="111">
@@ -3031,13 +3031,13 @@
         <v>13</v>
       </c>
       <c r="D111" t="n">
-        <v>36.7692307692308</v>
+        <v>36.9230769230769</v>
       </c>
       <c r="E111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F111" t="n">
-        <v>38.4615384615385</v>
+        <v>30.7692307692308</v>
       </c>
     </row>
     <row r="112">
@@ -3051,7 +3051,7 @@
         <v>13</v>
       </c>
       <c r="D112" t="n">
-        <v>36.3076923076923</v>
+        <v>35.3846153846154</v>
       </c>
       <c r="E112" t="n">
         <v>9</v>
@@ -3071,7 +3071,7 @@
         <v>12</v>
       </c>
       <c r="D113" t="n">
-        <v>32</v>
+        <v>31.9166666666667</v>
       </c>
       <c r="E113" t="n">
         <v>8</v>
@@ -3091,13 +3091,13 @@
         <v>12</v>
       </c>
       <c r="D114" t="n">
-        <v>25.25</v>
+        <v>25.1666666666667</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" t="n">
-        <v>66.6666666666667</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="D115" t="n">
-        <v>34.0909090909091</v>
+        <v>34.6363636363636</v>
       </c>
       <c r="E115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F115" t="n">
-        <v>27.2727272727273</v>
+        <v>18.1818181818182</v>
       </c>
     </row>
     <row r="116">
@@ -3131,13 +3131,13 @@
         <v>11</v>
       </c>
       <c r="D116" t="n">
-        <v>27.9090909090909</v>
+        <v>27.5454545454545</v>
       </c>
       <c r="E116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F116" t="n">
-        <v>45.4545454545455</v>
+        <v>54.5454545454545</v>
       </c>
     </row>
     <row r="117">
@@ -3151,7 +3151,7 @@
         <v>10</v>
       </c>
       <c r="D117" t="n">
-        <v>28.3</v>
+        <v>27.4</v>
       </c>
       <c r="E117" t="n">
         <v>5</v>
@@ -3171,7 +3171,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="n">
-        <v>32</v>
+        <v>31.7777777777778</v>
       </c>
       <c r="E118" t="n">
         <v>6</v>
@@ -3191,13 +3191,13 @@
         <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>27</v>
+        <v>28.2222222222222</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" t="n">
-        <v>77.7777777777778</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="120">
@@ -3211,13 +3211,13 @@
         <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>29</v>
+        <v>28.4444444444444</v>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>66.6666666666667</v>
+        <v>77.7777777777778</v>
       </c>
     </row>
     <row r="121">
@@ -3231,13 +3231,13 @@
         <v>8</v>
       </c>
       <c r="D121" t="n">
-        <v>36.375</v>
+        <v>35.375</v>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F121" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="122">
@@ -3251,7 +3251,7 @@
         <v>8</v>
       </c>
       <c r="D122" t="n">
-        <v>32.125</v>
+        <v>31</v>
       </c>
       <c r="E122" t="n">
         <v>6</v>
@@ -3271,7 +3271,7 @@
         <v>8</v>
       </c>
       <c r="D123" t="n">
-        <v>28.5</v>
+        <v>27.625</v>
       </c>
       <c r="E123" t="n">
         <v>3</v>
@@ -3291,13 +3291,13 @@
         <v>8</v>
       </c>
       <c r="D124" t="n">
-        <v>28.375</v>
+        <v>25.875</v>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F124" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125">
@@ -3311,13 +3311,13 @@
         <v>7</v>
       </c>
       <c r="D125" t="n">
-        <v>28.4285714285714</v>
+        <v>27.1428571428571</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>71.4285714285714</v>
+        <v>85.7142857142857</v>
       </c>
     </row>
     <row r="126">
@@ -3331,7 +3331,7 @@
         <v>7</v>
       </c>
       <c r="D126" t="n">
-        <v>29.5714285714286</v>
+        <v>29</v>
       </c>
       <c r="E126" t="n">
         <v>4</v>
@@ -3351,7 +3351,7 @@
         <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>31.3333333333333</v>
+        <v>31</v>
       </c>
       <c r="E127" t="n">
         <v>5</v>
@@ -3391,13 +3391,13 @@
         <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>30</v>
+        <v>29.3333333333333</v>
       </c>
       <c r="E129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F129" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="130">
@@ -3411,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>28.1666666666667</v>
+        <v>27.8333333333333</v>
       </c>
       <c r="E130" t="n">
         <v>3</v>
@@ -3431,13 +3431,13 @@
         <v>6</v>
       </c>
       <c r="D131" t="n">
-        <v>29.8333333333333</v>
+        <v>29.6666666666667</v>
       </c>
       <c r="E131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F131" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132">
@@ -3451,7 +3451,7 @@
         <v>6</v>
       </c>
       <c r="D132" t="n">
-        <v>32.3333333333333</v>
+        <v>32.6666666666667</v>
       </c>
       <c r="E132" t="n">
         <v>4</v>
@@ -3471,13 +3471,13 @@
         <v>6</v>
       </c>
       <c r="D133" t="n">
-        <v>25.6666666666667</v>
+        <v>25.8333333333333</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>83.3333333333333</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="134">
@@ -3491,13 +3491,13 @@
         <v>5</v>
       </c>
       <c r="D134" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135">
@@ -3511,7 +3511,7 @@
         <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>28.8</v>
+        <v>32.8</v>
       </c>
       <c r="E135" t="n">
         <v>3</v>
@@ -3531,13 +3531,13 @@
         <v>5</v>
       </c>
       <c r="D136" t="n">
-        <v>28.2</v>
+        <v>32</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="137">
@@ -3571,7 +3571,7 @@
         <v>4</v>
       </c>
       <c r="D138" t="n">
-        <v>28.75</v>
+        <v>28</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -3591,7 +3591,7 @@
         <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>34.25</v>
+        <v>33</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -3611,7 +3611,7 @@
         <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>29</v>
+        <v>27.6666666666667</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
@@ -3631,7 +3631,7 @@
         <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>31.3333333333333</v>
+        <v>30.3333333333333</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -3651,7 +3651,7 @@
         <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>35.3333333333333</v>
+        <v>34.3333333333333</v>
       </c>
       <c r="E142" t="n">
         <v>3</v>
@@ -3671,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -3691,13 +3691,13 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="145">
@@ -3731,7 +3731,7 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -3851,7 +3851,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -3911,7 +3911,7 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48A1B8B-29DE-4366-BFC7-96E2A555BEB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8594AA8C-2BE7-4D51-990F-4603E7EE2BC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBB88EA-E52C-4F02-8F82-F082B91528C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC7DF62C-16E6-4DE2-B937-E06EA6A8F2F7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858C418B-921E-4F80-BD71-9FA5A1530379}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4846AE20-40FF-4278-97E6-4F8468A7D9A5}"/>
 </file>
--- a/data/WP17/WP17_auswertung_sachgebiete.xlsx
+++ b/data/WP17/WP17_auswertung_sachgebiete.xlsx
@@ -854,10 +854,10 @@
         <v>31.5492371705964</v>
       </c>
       <c r="E2" t="n">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="F2" t="n">
-        <v>38.6962552011096</v>
+        <v>29.9583911234397</v>
       </c>
     </row>
     <row r="3">
@@ -874,10 +874,10 @@
         <v>34.3419170243205</v>
       </c>
       <c r="E3" t="n">
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="F3" t="n">
-        <v>33.3333333333333</v>
+        <v>24.7496423462089</v>
       </c>
     </row>
     <row r="4">
@@ -894,10 +894,10 @@
         <v>31.5639534883721</v>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="F4" t="n">
-        <v>29.0697674418605</v>
+        <v>25.3875968992248</v>
       </c>
     </row>
     <row r="5">
@@ -914,10 +914,10 @@
         <v>29.6713426853707</v>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="F5" t="n">
-        <v>43.2865731462926</v>
+        <v>41.0821643286573</v>
       </c>
     </row>
     <row r="6">
@@ -934,10 +934,10 @@
         <v>32.0049382716049</v>
       </c>
       <c r="E6" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="F6" t="n">
-        <v>32.0987654320988</v>
+        <v>28.3950617283951</v>
       </c>
     </row>
     <row r="7">
@@ -954,10 +954,10 @@
         <v>33.5915841584158</v>
       </c>
       <c r="E7" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="F7" t="n">
-        <v>28.2178217821782</v>
+        <v>24.5049504950495</v>
       </c>
     </row>
     <row r="8">
@@ -974,10 +974,10 @@
         <v>32.4617346938776</v>
       </c>
       <c r="E8" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="F8" t="n">
-        <v>32.6530612244898</v>
+        <v>26.7857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -994,10 +994,10 @@
         <v>29.7228260869565</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="F9" t="n">
-        <v>41.5760869565217</v>
+        <v>33.4239130434783</v>
       </c>
     </row>
     <row r="10">
@@ -1014,10 +1014,10 @@
         <v>32.0838150289017</v>
       </c>
       <c r="E10" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="F10" t="n">
-        <v>33.8150289017341</v>
+        <v>22.5433526011561</v>
       </c>
     </row>
     <row r="11">
@@ -1034,10 +1034,10 @@
         <v>31.4032786885246</v>
       </c>
       <c r="E11" t="n">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="F11" t="n">
-        <v>35.0819672131148</v>
+        <v>26.2295081967213</v>
       </c>
     </row>
     <row r="12">
@@ -1054,10 +1054,10 @@
         <v>30.701030927835</v>
       </c>
       <c r="E12" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F12" t="n">
-        <v>25.7731958762887</v>
+        <v>24.3986254295533</v>
       </c>
     </row>
     <row r="13">
@@ -1074,10 +1074,10 @@
         <v>30.9779411764706</v>
       </c>
       <c r="E13" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="F13" t="n">
-        <v>47.7941176470588</v>
+        <v>38.6029411764706</v>
       </c>
     </row>
     <row r="14">
@@ -1094,10 +1094,10 @@
         <v>36.6515837104072</v>
       </c>
       <c r="E14" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F14" t="n">
-        <v>19.0045248868778</v>
+        <v>16.289592760181</v>
       </c>
     </row>
     <row r="15">
@@ -1114,10 +1114,10 @@
         <v>34.203125</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>33.3333333333333</v>
+        <v>27.0833333333333</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>36.1375661375661</v>
       </c>
       <c r="E16" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F16" t="n">
-        <v>15.3439153439153</v>
+        <v>10.5820105820106</v>
       </c>
     </row>
     <row r="17">
@@ -1154,10 +1154,10 @@
         <v>32.6304347826087</v>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>36.4130434782609</v>
+        <v>30.9782608695652</v>
       </c>
     </row>
     <row r="18">
@@ -1174,10 +1174,10 @@
         <v>34.2191011235955</v>
       </c>
       <c r="E18" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F18" t="n">
-        <v>29.2134831460674</v>
+        <v>26.9662921348315</v>
       </c>
     </row>
     <row r="19">
@@ -1194,10 +1194,10 @@
         <v>32.1870967741935</v>
       </c>
       <c r="E19" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F19" t="n">
-        <v>18.0645161290323</v>
+        <v>14.1935483870968</v>
       </c>
     </row>
     <row r="20">
@@ -1214,10 +1214,10 @@
         <v>30.8896103896104</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F20" t="n">
-        <v>40.2597402597403</v>
+        <v>31.8181818181818</v>
       </c>
     </row>
     <row r="21">
@@ -1234,10 +1234,10 @@
         <v>31.1073825503356</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>44.2953020134228</v>
+        <v>32.8859060402685</v>
       </c>
     </row>
     <row r="22">
@@ -1274,10 +1274,10 @@
         <v>30.6170212765957</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
-        <v>48.936170212766</v>
+        <v>47.5177304964539</v>
       </c>
     </row>
     <row r="24">
@@ -1294,10 +1294,10 @@
         <v>31.6666666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F24" t="n">
-        <v>31.1594202898551</v>
+        <v>26.0869565217391</v>
       </c>
     </row>
     <row r="25">
@@ -1334,10 +1334,10 @@
         <v>30.8319327731092</v>
       </c>
       <c r="E26" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
-        <v>47.0588235294118</v>
+        <v>42.0168067226891</v>
       </c>
     </row>
     <row r="27">
@@ -1354,10 +1354,10 @@
         <v>32.6228070175439</v>
       </c>
       <c r="E27" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F27" t="n">
-        <v>24.5614035087719</v>
+        <v>14.9122807017544</v>
       </c>
     </row>
     <row r="28">
@@ -1374,10 +1374,10 @@
         <v>30.1315789473684</v>
       </c>
       <c r="E28" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>44.7368421052632</v>
+        <v>38.5964912280702</v>
       </c>
     </row>
     <row r="29">
@@ -1394,10 +1394,10 @@
         <v>29.0357142857143</v>
       </c>
       <c r="E29" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F29" t="n">
-        <v>48.2142857142857</v>
+        <v>46.4285714285714</v>
       </c>
     </row>
     <row r="30">
@@ -1414,10 +1414,10 @@
         <v>29.1923076923077</v>
       </c>
       <c r="E30" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F30" t="n">
-        <v>41.3461538461538</v>
+        <v>46.1538461538462</v>
       </c>
     </row>
     <row r="31">
@@ -1434,10 +1434,10 @@
         <v>35.6237623762376</v>
       </c>
       <c r="E31" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F31" t="n">
-        <v>17.8217821782178</v>
+        <v>16.8316831683168</v>
       </c>
     </row>
     <row r="32">
@@ -1454,10 +1454,10 @@
         <v>22.968085106383</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
-        <v>85.1063829787234</v>
+        <v>81.9148936170213</v>
       </c>
     </row>
     <row r="33">
@@ -1474,10 +1474,10 @@
         <v>26.2282608695652</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>65.2173913043478</v>
+        <v>61.9565217391304</v>
       </c>
     </row>
     <row r="34">
@@ -1494,10 +1494,10 @@
         <v>31.8539325842697</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F34" t="n">
-        <v>34.8314606741573</v>
+        <v>32.5842696629213</v>
       </c>
     </row>
     <row r="35">
@@ -1514,10 +1514,10 @@
         <v>31.9318181818182</v>
       </c>
       <c r="E35" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F35" t="n">
-        <v>32.9545454545455</v>
+        <v>22.7272727272727</v>
       </c>
     </row>
     <row r="36">
@@ -1534,10 +1534,10 @@
         <v>35.2413793103448</v>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F36" t="n">
-        <v>18.3908045977011</v>
+        <v>12.6436781609195</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>28.3448275862069</v>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
-        <v>60.9195402298851</v>
+        <v>49.4252873563218</v>
       </c>
     </row>
     <row r="38">
@@ -1574,10 +1574,10 @@
         <v>31.8928571428571</v>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F38" t="n">
-        <v>42.8571428571429</v>
+        <v>29.7619047619048</v>
       </c>
     </row>
     <row r="39">
@@ -1594,10 +1594,10 @@
         <v>29.2168674698795</v>
       </c>
       <c r="E39" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F39" t="n">
-        <v>53.0120481927711</v>
+        <v>43.3734939759036</v>
       </c>
     </row>
     <row r="40">
@@ -1614,10 +1614,10 @@
         <v>25.3414634146341</v>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F40" t="n">
-        <v>69.5121951219512</v>
+        <v>67.0731707317073</v>
       </c>
     </row>
     <row r="41">
@@ -1634,10 +1634,10 @@
         <v>31.7283950617284</v>
       </c>
       <c r="E41" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>35.8024691358025</v>
+        <v>27.1604938271605</v>
       </c>
     </row>
     <row r="42">
@@ -1654,10 +1654,10 @@
         <v>31.6625</v>
       </c>
       <c r="E42" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F42" t="n">
-        <v>27.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="43">
@@ -1674,10 +1674,10 @@
         <v>31.3589743589744</v>
       </c>
       <c r="E43" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F43" t="n">
-        <v>29.4871794871795</v>
+        <v>26.9230769230769</v>
       </c>
     </row>
     <row r="44">
@@ -1694,10 +1694,10 @@
         <v>27.3815789473684</v>
       </c>
       <c r="E44" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F44" t="n">
-        <v>69.7368421052632</v>
+        <v>61.8421052631579</v>
       </c>
     </row>
     <row r="45">
@@ -1714,10 +1714,10 @@
         <v>34.1447368421053</v>
       </c>
       <c r="E45" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>21.0526315789474</v>
       </c>
     </row>
     <row r="46">
@@ -1734,10 +1734,10 @@
         <v>39.1917808219178</v>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F46" t="n">
-        <v>10.958904109589</v>
+        <v>6.84931506849315</v>
       </c>
     </row>
     <row r="47">
@@ -1754,10 +1754,10 @@
         <v>33.9718309859155</v>
       </c>
       <c r="E47" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F47" t="n">
-        <v>33.8028169014084</v>
+        <v>26.7605633802817</v>
       </c>
     </row>
     <row r="48">
@@ -1774,10 +1774,10 @@
         <v>24.6571428571429</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>92.8571428571429</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
@@ -1794,10 +1794,10 @@
         <v>31.231884057971</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F49" t="n">
-        <v>39.1304347826087</v>
+        <v>31.8840579710145</v>
       </c>
     </row>
     <row r="50">
@@ -1814,10 +1814,10 @@
         <v>31.865671641791</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>37.3134328358209</v>
+        <v>26.865671641791</v>
       </c>
     </row>
     <row r="51">
@@ -1834,10 +1834,10 @@
         <v>35.640625</v>
       </c>
       <c r="E51" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F51" t="n">
-        <v>15.625</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="52">
@@ -1854,10 +1854,10 @@
         <v>32.1428571428571</v>
       </c>
       <c r="E52" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
-        <v>38.0952380952381</v>
+        <v>31.7460317460317</v>
       </c>
     </row>
     <row r="53">
@@ -1874,10 +1874,10 @@
         <v>31.258064516129</v>
       </c>
       <c r="E53" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>40.3225806451613</v>
+        <v>20.9677419354839</v>
       </c>
     </row>
     <row r="54">
@@ -1894,10 +1894,10 @@
         <v>33.6935483870968</v>
       </c>
       <c r="E54" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F54" t="n">
-        <v>40.3225806451613</v>
+        <v>25.8064516129032</v>
       </c>
     </row>
     <row r="55">
@@ -1914,10 +1914,10 @@
         <v>32.0819672131148</v>
       </c>
       <c r="E55" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
-        <v>40.983606557377</v>
+        <v>31.1475409836066</v>
       </c>
     </row>
     <row r="56">
@@ -1934,10 +1934,10 @@
         <v>31.1666666666667</v>
       </c>
       <c r="E56" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
-        <v>31.6666666666667</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -1954,10 +1954,10 @@
         <v>32.4833333333333</v>
       </c>
       <c r="E57" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F57" t="n">
-        <v>31.6666666666667</v>
+        <v>26.6666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -1974,10 +1974,10 @@
         <v>37.5762711864407</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>15.2542372881356</v>
+        <v>13.5593220338983</v>
       </c>
     </row>
     <row r="59">
@@ -1994,10 +1994,10 @@
         <v>29.9818181818182</v>
       </c>
       <c r="E59" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>43.6363636363636</v>
+        <v>32.7272727272727</v>
       </c>
     </row>
     <row r="60">
@@ -2014,10 +2014,10 @@
         <v>30.037037037037</v>
       </c>
       <c r="E60" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>42.5925925925926</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="61">
@@ -2054,10 +2054,10 @@
         <v>29.7692307692308</v>
       </c>
       <c r="E62" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>40.3846153846154</v>
+        <v>26.9230769230769</v>
       </c>
     </row>
     <row r="63">
@@ -2074,10 +2074,10 @@
         <v>28.28</v>
       </c>
       <c r="E63" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
@@ -2094,10 +2094,10 @@
         <v>34.1666666666667</v>
       </c>
       <c r="E64" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F64" t="n">
-        <v>27.0833333333333</v>
+        <v>22.9166666666667</v>
       </c>
     </row>
     <row r="65">
@@ -2114,10 +2114,10 @@
         <v>31.2857142857143</v>
       </c>
       <c r="E65" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F65" t="n">
-        <v>33.3333333333333</v>
+        <v>26.1904761904762</v>
       </c>
     </row>
     <row r="66">
@@ -2134,10 +2134,10 @@
         <v>30.1219512195122</v>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F66" t="n">
-        <v>53.6585365853659</v>
+        <v>51.219512195122</v>
       </c>
     </row>
     <row r="67">
@@ -2174,10 +2174,10 @@
         <v>33</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F68" t="n">
-        <v>36.8421052631579</v>
+        <v>31.5789473684211</v>
       </c>
     </row>
     <row r="69">
@@ -2194,10 +2194,10 @@
         <v>31.8378378378378</v>
       </c>
       <c r="E69" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
-        <v>40.5405405405405</v>
+        <v>35.1351351351351</v>
       </c>
     </row>
     <row r="70">
@@ -2214,10 +2214,10 @@
         <v>35.5945945945946</v>
       </c>
       <c r="E70" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F70" t="n">
-        <v>29.7297297297297</v>
+        <v>18.9189189189189</v>
       </c>
     </row>
     <row r="71">
@@ -2234,10 +2234,10 @@
         <v>30.9722222222222</v>
       </c>
       <c r="E71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>27.7777777777778</v>
       </c>
     </row>
     <row r="72">
@@ -2254,10 +2254,10 @@
         <v>29</v>
       </c>
       <c r="E72" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F72" t="n">
-        <v>57.1428571428571</v>
+        <v>34.2857142857143</v>
       </c>
     </row>
     <row r="73">
@@ -2274,10 +2274,10 @@
         <v>34.1142857142857</v>
       </c>
       <c r="E73" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F73" t="n">
-        <v>22.8571428571428</v>
+        <v>17.1428571428571</v>
       </c>
     </row>
     <row r="74">
@@ -2294,10 +2294,10 @@
         <v>32.3333333333333</v>
       </c>
       <c r="E74" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
-        <v>36.3636363636364</v>
+        <v>27.2727272727273</v>
       </c>
     </row>
     <row r="75">
@@ -2314,10 +2314,10 @@
         <v>30.9090909090909</v>
       </c>
       <c r="E75" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F75" t="n">
-        <v>30.3030303030303</v>
+        <v>21.2121212121212</v>
       </c>
     </row>
     <row r="76">
@@ -2334,10 +2334,10 @@
         <v>31.2727272727273</v>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F76" t="n">
-        <v>33.3333333333333</v>
+        <v>24.2424242424242</v>
       </c>
     </row>
     <row r="77">
@@ -2354,10 +2354,10 @@
         <v>29.030303030303</v>
       </c>
       <c r="E77" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F77" t="n">
-        <v>57.5757575757576</v>
+        <v>36.3636363636364</v>
       </c>
     </row>
     <row r="78">
@@ -2394,10 +2394,10 @@
         <v>32.3548387096774</v>
       </c>
       <c r="E79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
-        <v>29.0322580645161</v>
+        <v>22.5806451612903</v>
       </c>
     </row>
     <row r="80">
@@ -2414,10 +2414,10 @@
         <v>36.2903225806452</v>
       </c>
       <c r="E80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F80" t="n">
-        <v>35.4838709677419</v>
+        <v>32.258064516129</v>
       </c>
     </row>
     <row r="81">
@@ -2434,10 +2434,10 @@
         <v>28.5333333333333</v>
       </c>
       <c r="E81" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F81" t="n">
-        <v>63.3333333333333</v>
+        <v>53.3333333333333</v>
       </c>
     </row>
     <row r="82">
@@ -2454,10 +2454,10 @@
         <v>29.6896551724138</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
-        <v>48.2758620689655</v>
+        <v>31.0344827586207</v>
       </c>
     </row>
     <row r="83">
@@ -2474,10 +2474,10 @@
         <v>29.7241379310345</v>
       </c>
       <c r="E83" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>51.7241379310345</v>
+        <v>37.9310344827586</v>
       </c>
     </row>
     <row r="84">
@@ -2494,10 +2494,10 @@
         <v>30.2592592592593</v>
       </c>
       <c r="E84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F84" t="n">
-        <v>40.7407407407407</v>
+        <v>37.037037037037</v>
       </c>
     </row>
     <row r="85">
@@ -2514,10 +2514,10 @@
         <v>34.5769230769231</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F85" t="n">
-        <v>26.9230769230769</v>
+        <v>11.5384615384615</v>
       </c>
     </row>
     <row r="86">
@@ -2534,10 +2534,10 @@
         <v>35.7692307692308</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F86" t="n">
-        <v>30.7692307692308</v>
+        <v>19.2307692307692</v>
       </c>
     </row>
     <row r="87">
@@ -2554,10 +2554,10 @@
         <v>32.8846153846154</v>
       </c>
       <c r="E87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F87" t="n">
-        <v>23.0769230769231</v>
+        <v>15.3846153846154</v>
       </c>
     </row>
     <row r="88">
@@ -2574,10 +2574,10 @@
         <v>32.5384615384615</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F88" t="n">
-        <v>42.3076923076923</v>
+        <v>19.2307692307692</v>
       </c>
     </row>
     <row r="89">
@@ -2594,10 +2594,10 @@
         <v>34.12</v>
       </c>
       <c r="E89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F89" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90">
@@ -2614,10 +2614,10 @@
         <v>34.56</v>
       </c>
       <c r="E90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
@@ -2634,10 +2634,10 @@
         <v>32.3913043478261</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F91" t="n">
-        <v>47.8260869565217</v>
+        <v>39.1304347826087</v>
       </c>
     </row>
     <row r="92">
@@ -2654,10 +2654,10 @@
         <v>32.2380952380952</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
-        <v>42.8571428571429</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="93">
@@ -2674,10 +2674,10 @@
         <v>32.7142857142857</v>
       </c>
       <c r="E93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
-        <v>19.047619047619</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="94">
@@ -2694,10 +2694,10 @@
         <v>33.25</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F94" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -2714,10 +2714,10 @@
         <v>30.7894736842105</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>36.8421052631579</v>
+        <v>31.5789473684211</v>
       </c>
     </row>
     <row r="96">
@@ -2734,10 +2734,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F96" t="n">
-        <v>50</v>
+        <v>38.8888888888889</v>
       </c>
     </row>
     <row r="97">
@@ -2754,10 +2754,10 @@
         <v>29.3333333333333</v>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F97" t="n">
-        <v>50</v>
+        <v>38.8888888888889</v>
       </c>
     </row>
     <row r="98">
@@ -2774,10 +2774,10 @@
         <v>37.125</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2794,10 +2794,10 @@
         <v>27</v>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F99" t="n">
-        <v>68.75</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="100">
@@ -2814,10 +2814,10 @@
         <v>30.0625</v>
       </c>
       <c r="E100" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F100" t="n">
-        <v>50</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="101">
@@ -2834,10 +2834,10 @@
         <v>36.4375</v>
       </c>
       <c r="E101" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>18.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="102">
@@ -2854,10 +2854,10 @@
         <v>24.9375</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>81.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
@@ -2914,10 +2914,10 @@
         <v>27.5</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F105" t="n">
-        <v>71.4285714285714</v>
+        <v>64.2857142857143</v>
       </c>
     </row>
     <row r="106">
@@ -2934,10 +2934,10 @@
         <v>30.0714285714286</v>
       </c>
       <c r="E106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F106" t="n">
-        <v>50</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="107">
@@ -2954,10 +2954,10 @@
         <v>30.2857142857143</v>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F107" t="n">
-        <v>57.1428571428571</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="108">
@@ -2974,10 +2974,10 @@
         <v>32.6428571428571</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F108" t="n">
-        <v>21.4285714285714</v>
+        <v>7.14285714285714</v>
       </c>
     </row>
     <row r="109">
@@ -3014,10 +3014,10 @@
         <v>25.3076923076923</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F110" t="n">
-        <v>76.9230769230769</v>
+        <v>69.2307692307692</v>
       </c>
     </row>
     <row r="111">
@@ -3034,10 +3034,10 @@
         <v>36.9230769230769</v>
       </c>
       <c r="E111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F111" t="n">
-        <v>30.7692307692308</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="112">
@@ -3054,10 +3054,10 @@
         <v>35.3846153846154</v>
       </c>
       <c r="E112" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F112" t="n">
-        <v>30.7692307692308</v>
+        <v>7.69230769230769</v>
       </c>
     </row>
     <row r="113">
@@ -3094,10 +3094,10 @@
         <v>25.1666666666667</v>
       </c>
       <c r="E114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F114" t="n">
-        <v>75</v>
+        <v>58.3333333333333</v>
       </c>
     </row>
     <row r="115">
@@ -3114,10 +3114,10 @@
         <v>34.6363636363636</v>
       </c>
       <c r="E115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>18.1818181818182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3134,10 +3134,10 @@
         <v>27.5454545454545</v>
       </c>
       <c r="E116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F116" t="n">
-        <v>54.5454545454545</v>
+        <v>45.4545454545455</v>
       </c>
     </row>
     <row r="117">
@@ -3274,10 +3274,10 @@
         <v>27.625</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124">
@@ -3314,10 +3314,10 @@
         <v>27.1428571428571</v>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" t="n">
-        <v>85.7142857142857</v>
+        <v>71.4285714285714</v>
       </c>
     </row>
     <row r="126">
@@ -3334,10 +3334,10 @@
         <v>29</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F126" t="n">
-        <v>42.8571428571429</v>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="127">
@@ -3354,10 +3354,10 @@
         <v>31</v>
       </c>
       <c r="E127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F127" t="n">
-        <v>16.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3394,10 +3394,10 @@
         <v>29.3333333333333</v>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F129" t="n">
-        <v>50</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="130">
@@ -3414,10 +3414,10 @@
         <v>27.8333333333333</v>
       </c>
       <c r="E130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F130" t="n">
-        <v>50</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="131">
@@ -3434,10 +3434,10 @@
         <v>29.6666666666667</v>
       </c>
       <c r="E131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F131" t="n">
-        <v>50</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="132">
@@ -3474,10 +3474,10 @@
         <v>25.8333333333333</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="134">
@@ -3494,10 +3494,10 @@
         <v>28.2</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135">
@@ -3794,10 +3794,10 @@
         <v>28</v>
       </c>
       <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
         <v>0</v>
-      </c>
-      <c r="F149" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="150">
@@ -3834,10 +3834,10 @@
         <v>28</v>
       </c>
       <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
         <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="152">
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8594AA8C-2BE7-4D51-990F-4603E7EE2BC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4E26D61-CA9E-4B00-AE0D-2F0FA2D7EEB1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC7DF62C-16E6-4DE2-B937-E06EA6A8F2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAE0CC7E-2FC7-46D2-8138-30AC86727D65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4846AE20-40FF-4278-97E6-4F8468A7D9A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A171242-A03E-4AC9-BD5B-B929EDDAA2FC}"/>
 </file>